--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-1-viskositaet.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-1-viskositaet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1750,6 +1750,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1868,6 +1875,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12835,7 +12846,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12893,7 +12904,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12904,10 +12915,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13019,10 +13030,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13136,10 +13147,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13255,10 +13266,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13284,13 +13295,13 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>261</v>
@@ -13342,7 +13353,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13360,7 +13371,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>266</v>
@@ -13374,10 +13385,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13400,16 +13411,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>386</v>
@@ -13461,7 +13472,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13479,7 +13490,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>389</v>
@@ -13493,10 +13504,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13522,13 +13533,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>435</v>
@@ -13580,7 +13591,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13612,10 +13623,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13641,10 +13652,10 @@
         <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>444</v>
@@ -13699,7 +13710,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13731,10 +13742,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13760,10 +13771,10 @@
         <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>495</v>
@@ -13818,7 +13829,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13850,13 +13861,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
@@ -13881,10 +13892,10 @@
         <v>492</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>553</v>
@@ -13960,7 +13971,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -13971,10 +13982,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14086,10 +14097,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14203,10 +14214,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14322,10 +14333,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14351,13 +14362,13 @@
         <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>261</v>
@@ -14409,7 +14420,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14427,7 +14438,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>266</v>
@@ -14441,10 +14452,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14556,10 +14567,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14673,10 +14684,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14748,7 +14759,7 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
@@ -14790,10 +14801,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>309</v>
@@ -14909,10 +14920,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>321</v>
@@ -15028,10 +15039,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15147,10 +15158,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15173,16 +15184,16 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>386</v>
@@ -15222,7 +15233,7 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
@@ -15232,7 +15243,7 @@
         <v>117</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15250,7 +15261,7 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>389</v>
@@ -15264,13 +15275,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -15295,13 +15306,13 @@
         <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>386</v>
@@ -15353,7 +15364,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15371,7 +15382,7 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>389</v>
@@ -15385,10 +15396,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15500,10 +15511,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15617,10 +15628,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15736,10 +15747,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15855,10 +15866,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15972,10 +15983,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16089,10 +16100,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16208,10 +16219,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16237,13 +16248,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>435</v>
@@ -16295,7 +16306,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16327,10 +16338,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16356,10 +16367,10 @@
         <v>232</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>444</v>
@@ -16414,7 +16425,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16446,10 +16457,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16475,10 +16486,10 @@
         <v>82</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>495</v>
@@ -16533,7 +16544,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16565,13 +16576,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -16596,10 +16607,10 @@
         <v>492</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>553</v>
@@ -16675,7 +16686,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16686,10 +16697,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16801,10 +16812,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16918,10 +16929,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17037,10 +17048,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17066,13 +17077,13 @@
         <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>261</v>
@@ -17124,7 +17135,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>91</v>
@@ -17142,7 +17153,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>266</v>
@@ -17156,10 +17167,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17271,10 +17282,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17388,10 +17399,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17463,7 +17474,7 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
@@ -17505,10 +17516,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>309</v>
@@ -17624,10 +17635,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>321</v>
@@ -17743,10 +17754,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17862,10 +17873,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17888,16 +17899,16 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>386</v>
@@ -17937,7 +17948,7 @@
         <v>81</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -17947,7 +17958,7 @@
         <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17965,7 +17976,7 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>389</v>
@@ -17979,13 +17990,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>81</v>
@@ -18010,13 +18021,13 @@
         <v>382</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O133" t="s" s="2">
         <v>386</v>
@@ -18068,7 +18079,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18086,7 +18097,7 @@
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>389</v>
@@ -18100,10 +18111,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18215,10 +18226,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18332,10 +18343,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18451,10 +18462,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18570,10 +18581,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18616,7 +18627,7 @@
         <v>81</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>81</v>
@@ -18687,10 +18698,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18804,10 +18815,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18852,7 +18863,7 @@
         <v>81</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>81</v>
@@ -18923,10 +18934,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18952,13 +18963,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>435</v>
@@ -19010,7 +19021,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19042,10 +19053,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19071,10 +19082,10 @@
         <v>232</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>444</v>
@@ -19129,7 +19140,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19161,10 +19172,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19190,10 +19201,10 @@
         <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>495</v>
@@ -19248,7 +19259,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19280,13 +19291,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19311,10 +19322,10 @@
         <v>492</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>553</v>
@@ -19390,7 +19401,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -19401,10 +19412,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19516,10 +19527,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19633,10 +19644,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19752,10 +19763,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19781,13 +19792,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>261</v>
@@ -19839,7 +19850,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>91</v>
@@ -19857,7 +19868,7 @@
         <v>81</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>266</v>
@@ -19871,10 +19882,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19986,10 +19997,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20103,10 +20114,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20178,7 +20189,7 @@
         <v>81</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -20220,10 +20231,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>309</v>
@@ -20270,7 +20281,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20339,10 +20350,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20458,10 +20469,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20484,16 +20495,16 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>386</v>
@@ -20545,7 +20556,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20563,7 +20574,7 @@
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>389</v>
@@ -20577,10 +20588,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20606,13 +20617,13 @@
         <v>232</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>435</v>
@@ -20664,7 +20675,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20696,10 +20707,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20725,10 +20736,10 @@
         <v>232</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>444</v>
@@ -20783,7 +20794,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20815,10 +20826,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20844,10 +20855,10 @@
         <v>82</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>495</v>
@@ -20902,7 +20913,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-1-viskositaet.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-1-viskositaet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -1304,7 +1304,7 @@
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
-    <t>/kPA*s</t>
+    <t>/(kPa.s)</t>
   </si>
   <si>
     <t>Quantity.unit</t>
@@ -1348,9 +1348,6 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>/kPA.s</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -10496,46 +10493,46 @@
         <v>81</v>
       </c>
       <c r="S69" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10567,10 +10564,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10596,16 +10593,16 @@
         <v>232</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10633,37 +10630,37 @@
         <v>148</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI70" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>103</v>
@@ -10675,7 +10672,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10686,14 +10683,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10715,16 +10712,16 @@
         <v>232</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10752,11 +10749,11 @@
         <v>148</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10773,7 +10770,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10791,24 +10788,24 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10831,19 +10828,19 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10892,7 +10889,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10913,7 +10910,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10924,10 +10921,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10953,13 +10950,13 @@
         <v>232</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10988,11 +10985,11 @@
         <v>156</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
       </c>
@@ -11009,7 +11006,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11027,24 +11024,24 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11070,16 +11067,16 @@
         <v>232</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11107,11 +11104,11 @@
         <v>156</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11128,7 +11125,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11149,7 +11146,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11160,10 +11157,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11186,16 +11183,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11245,7 +11242,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11263,24 +11260,24 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11303,16 +11300,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11362,7 +11359,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11380,24 +11377,24 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>490</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11420,19 +11417,19 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11481,7 +11478,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11493,16 +11490,16 @@
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11513,10 +11510,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11628,10 +11625,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11745,14 +11742,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11774,10 +11771,10 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>114</v>
@@ -11832,7 +11829,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11864,10 +11861,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11890,13 +11887,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11947,7 +11944,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11956,7 +11953,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11968,7 +11965,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11979,10 +11976,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12005,13 +12002,13 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12062,7 +12059,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12071,7 +12068,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -12083,7 +12080,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12094,10 +12091,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12123,16 +12120,16 @@
         <v>232</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12160,11 +12157,11 @@
         <v>170</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12181,7 +12178,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12199,10 +12196,10 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -12213,10 +12210,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12242,16 +12239,16 @@
         <v>232</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12279,11 +12276,11 @@
         <v>156</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12300,7 +12297,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12318,10 +12315,10 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -12332,10 +12329,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12358,17 +12355,17 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12417,7 +12414,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12449,10 +12446,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12478,10 +12475,10 @@
         <v>105</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12532,7 +12529,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12553,7 +12550,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12564,10 +12561,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12590,16 +12587,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12649,7 +12646,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12670,7 +12667,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12681,10 +12678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12707,16 +12704,16 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12766,7 +12763,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12787,7 +12784,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12798,10 +12795,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12824,19 +12821,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12846,7 +12843,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12883,7 +12880,7 @@
         <v>117</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12904,7 +12901,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12915,10 +12912,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13030,10 +13027,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13147,14 +13144,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13176,10 +13173,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>114</v>
@@ -13234,7 +13231,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13266,10 +13263,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13295,13 +13292,13 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>261</v>
@@ -13353,7 +13350,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13371,7 +13368,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>266</v>
@@ -13385,10 +13382,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13411,16 +13408,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>386</v>
@@ -13472,7 +13469,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13490,7 +13487,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>389</v>
@@ -13504,10 +13501,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13533,16 +13530,16 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13570,37 +13567,37 @@
         <v>148</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z95" t="s" s="2">
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>103</v>
@@ -13612,7 +13609,7 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
@@ -13623,14 +13620,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13652,16 +13649,16 @@
         <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N96" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13689,11 +13686,11 @@
         <v>148</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13710,7 +13707,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13728,24 +13725,24 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13771,16 +13768,16 @@
         <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N97" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13829,7 +13826,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13850,7 +13847,7 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
@@ -13861,13 +13858,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
@@ -13889,19 +13886,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>584</v>
-      </c>
       <c r="N98" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O98" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13950,7 +13947,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13971,7 +13968,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -13982,10 +13979,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14097,10 +14094,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14214,14 +14211,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14243,10 +14240,10 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>114</v>
@@ -14301,7 +14298,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14333,10 +14330,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14362,13 +14359,13 @@
         <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>261</v>
@@ -14420,7 +14417,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14438,7 +14435,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>266</v>
@@ -14452,10 +14449,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14567,10 +14564,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14684,10 +14681,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14759,7 +14756,7 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
@@ -14801,10 +14798,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>309</v>
@@ -14920,10 +14917,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>321</v>
@@ -15039,10 +15036,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15158,10 +15155,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15184,16 +15181,16 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>386</v>
@@ -15233,7 +15230,7 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
@@ -15243,7 +15240,7 @@
         <v>117</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15261,7 +15258,7 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>389</v>
@@ -15275,13 +15272,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C110" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -15306,13 +15303,13 @@
         <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>386</v>
@@ -15364,7 +15361,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15382,7 +15379,7 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>389</v>
@@ -15396,10 +15393,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15511,10 +15508,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15628,10 +15625,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15747,10 +15744,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15866,10 +15863,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15912,7 +15909,7 @@
         <v>81</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>81</v>
@@ -15983,10 +15980,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16100,10 +16097,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16148,46 +16145,46 @@
         <v>81</v>
       </c>
       <c r="S117" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16219,10 +16216,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16248,16 +16245,16 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N118" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="O118" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16285,37 +16282,37 @@
         <v>148</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z118" t="s" s="2">
+      <c r="AA118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>103</v>
@@ -16327,7 +16324,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -16338,14 +16335,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16367,16 +16364,16 @@
         <v>232</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M119" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N119" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O119" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -16404,11 +16401,11 @@
         <v>148</v>
       </c>
       <c r="Y119" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z119" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z119" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
       </c>
@@ -16425,7 +16422,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16443,24 +16440,24 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM119" t="s" s="2">
+      <c r="AN119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO119" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16486,16 +16483,16 @@
         <v>82</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M120" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N120" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O120" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16544,7 +16541,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16565,7 +16562,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16576,13 +16573,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -16604,19 +16601,19 @@
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M121" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="N121" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O121" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16665,7 +16662,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16686,7 +16683,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16697,10 +16694,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16812,10 +16809,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16929,14 +16926,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16958,10 +16955,10 @@
         <v>111</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>114</v>
@@ -17016,7 +17013,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17048,10 +17045,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17077,13 +17074,13 @@
         <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>261</v>
@@ -17135,7 +17132,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>91</v>
@@ -17153,7 +17150,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>266</v>
@@ -17167,10 +17164,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17282,10 +17279,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17399,10 +17396,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17474,7 +17471,7 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
@@ -17516,10 +17513,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>309</v>
@@ -17635,10 +17632,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>321</v>
@@ -17754,10 +17751,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17873,10 +17870,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17899,16 +17896,16 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>386</v>
@@ -17948,7 +17945,7 @@
         <v>81</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -17958,7 +17955,7 @@
         <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17976,7 +17973,7 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>389</v>
@@ -17990,13 +17987,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>81</v>
@@ -18021,13 +18018,13 @@
         <v>382</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O133" t="s" s="2">
         <v>386</v>
@@ -18079,7 +18076,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18097,7 +18094,7 @@
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>389</v>
@@ -18111,10 +18108,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18226,10 +18223,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18343,10 +18340,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18462,10 +18459,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18581,10 +18578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18627,7 +18624,7 @@
         <v>81</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>81</v>
@@ -18698,10 +18695,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18815,10 +18812,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18863,7 +18860,7 @@
         <v>81</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>81</v>
@@ -18902,7 +18899,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18934,10 +18931,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18963,16 +18960,16 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N141" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="O141" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19000,37 +18997,37 @@
         <v>148</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z141" t="s" s="2">
+      <c r="AA141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI141" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>103</v>
@@ -19042,7 +19039,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19053,14 +19050,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19082,16 +19079,16 @@
         <v>232</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M142" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N142" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O142" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19119,11 +19116,11 @@
         <v>148</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19140,7 +19137,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19158,24 +19155,24 @@
         <v>81</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM142" t="s" s="2">
+      <c r="AN142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19201,16 +19198,16 @@
         <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M143" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N143" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O143" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19259,7 +19256,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19280,7 +19277,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19291,13 +19288,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C144" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19319,19 +19316,19 @@
         <v>92</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M144" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="N144" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O144" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>81</v>
@@ -19380,7 +19377,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19401,7 +19398,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -19412,10 +19409,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19527,10 +19524,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19644,14 +19641,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -19673,10 +19670,10 @@
         <v>111</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>114</v>
@@ -19731,7 +19728,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19763,10 +19760,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19792,13 +19789,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>261</v>
@@ -19850,7 +19847,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>91</v>
@@ -19868,7 +19865,7 @@
         <v>81</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>266</v>
@@ -19882,10 +19879,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19997,10 +19994,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20114,10 +20111,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20189,7 +20186,7 @@
         <v>81</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -20231,10 +20228,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>309</v>
@@ -20281,7 +20278,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20350,10 +20347,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20469,10 +20466,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20495,16 +20492,16 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>386</v>
@@ -20556,7 +20553,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20574,7 +20571,7 @@
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>389</v>
@@ -20588,10 +20585,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20617,16 +20614,16 @@
         <v>232</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N155" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="O155" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -20654,37 +20651,37 @@
         <v>148</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z155" t="s" s="2">
+      <c r="AA155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI155" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>103</v>
@@ -20696,7 +20693,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -20707,14 +20704,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -20736,16 +20733,16 @@
         <v>232</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M156" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N156" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O156" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -20773,11 +20770,11 @@
         <v>148</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
       </c>
@@ -20794,7 +20791,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20812,24 +20809,24 @@
         <v>81</v>
       </c>
       <c r="AL156" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM156" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM156" t="s" s="2">
+      <c r="AN156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO156" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20855,16 +20852,16 @@
         <v>82</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M157" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N157" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O157" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -20913,7 +20910,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20934,7 +20931,7 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
